--- a/sampleprojects/TaxReturn/excel/states/TN.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/TN.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>DT: TN Tax</t>
   </si>
@@ -41,28 +41,19 @@
     <t>DSL: INITIAL ACTIONS</t>
   </si>
   <si>
+    <t>CONDITIONS: COMMENTS</t>
+  </si>
+  <si>
+    <t>DSL: CONDITIONS</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>set result.tn_tax = 0; add "  Tennessee (no state income tax)" to job.audit_trail</t>
-  </si>
-  <si>
-    <t>CONDITIONS: COMMENTS</t>
-  </si>
-  <si>
-    <t>DSL: CONDITIONS</t>
-  </si>
-  <si>
-    <t>Married Filing Jointly</t>
-  </si>
-  <si>
-    <t>job.filing_status == "married_filing_jointly"</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>N</t>
+    <t>perform when called</t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
   <si>
     <t>ACTIONS: COMMENTS</t>
@@ -71,28 +62,13 @@
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>Calculate TN tax MFJ. NOTE: TN has no state income tax (2025) — actual state tax is $0. Postfix retains legacy hypothetical-bracket logic referencing TN constants not in TN_edd; EL form below honors no-income-tax acceptance criterion.</t>
-  </si>
-  <si>
-    <t>set result.tn_tax = 0; add "  TN has no state income tax: $0" to job.audit_trail</t>
+    <t>No income tax: the roster pass resets result.computed_state_tax to zero before dispatching here, so the only thing to do is say so. The table used to assign a result field no EDD declared, which nothing noticed because the old dispatcher never performed it (#1177)</t>
+  </si>
+  <si>
+    <t>add "  Tennessee (no state income tax)" to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>
-  </si>
-  <si>
-    <t>Calculate TN tax Single/other. NOTE: TN has no state income tax (2025) — actual state tax is $0. Postfix retains legacy hypothetical-bracket logic referencing TN constants not in TN_edd; EL form below honors no-income-tax acceptance criterion.</t>
-  </si>
-  <si>
-    <t>Policy:</t>
-  </si>
-  <si>
-    <t>Policy Statements</t>
-  </si>
-  <si>
-    <t>Calculate Tennessee tax MFJ</t>
-  </si>
-  <si>
-    <t>Calculate Tennessee tax Single/other</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -763,501 +739,240 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9">
-      <c r="A9" s="5">
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="L10" s="1">
         <v>9</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
+      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1">
+        <v>12</v>
+      </c>
+      <c r="P10" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>14</v>
+      </c>
+      <c r="R10" s="1">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1">
+        <v>16</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1" t="s">
+      <c r="A11" s="5">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E13" s="4">
         <v>2</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F13" s="4">
         <v>3</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G13" s="4">
         <v>4</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H13" s="4">
         <v>5</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I13" s="4">
         <v>6</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J13" s="4">
         <v>7</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K13" s="4">
         <v>8</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L13" s="4">
         <v>9</v>
       </c>
-      <c r="M11" s="1">
-        <v>10</v>
-      </c>
-      <c r="N11" s="1">
+      <c r="M13" s="4">
+        <v>10</v>
+      </c>
+      <c r="N13" s="4">
         <v>11</v>
       </c>
-      <c r="O11" s="1">
+      <c r="O13" s="4">
         <v>12</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P13" s="4">
         <v>13</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q13" s="4">
         <v>14</v>
       </c>
-      <c r="R11" s="1">
+      <c r="R13" s="4">
         <v>15</v>
       </c>
-      <c r="S11" s="1">
+      <c r="S13" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5">
+    <row r="14">
+      <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4">
-        <v>2</v>
-      </c>
-      <c r="F14" s="4">
-        <v>3</v>
-      </c>
-      <c r="G14" s="4">
-        <v>4</v>
-      </c>
-      <c r="H14" s="4">
-        <v>5</v>
-      </c>
-      <c r="I14" s="4">
-        <v>6</v>
-      </c>
-      <c r="J14" s="4">
-        <v>7</v>
-      </c>
-      <c r="K14" s="4">
-        <v>8</v>
-      </c>
-      <c r="L14" s="4">
-        <v>9</v>
-      </c>
-      <c r="M14" s="4">
-        <v>10</v>
-      </c>
-      <c r="N14" s="4">
-        <v>11</v>
-      </c>
-      <c r="O14" s="4">
-        <v>12</v>
-      </c>
-      <c r="P14" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>14</v>
-      </c>
-      <c r="R14" s="4">
-        <v>15</v>
-      </c>
-      <c r="S14" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5">
-        <v>1</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5">
-        <v>2</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1">
-        <v>2</v>
-      </c>
-      <c r="F18" s="1">
-        <v>3</v>
-      </c>
-      <c r="G18" s="1">
-        <v>4</v>
-      </c>
-      <c r="H18" s="1">
-        <v>5</v>
-      </c>
-      <c r="I18" s="1">
-        <v>6</v>
-      </c>
-      <c r="J18" s="1">
-        <v>7</v>
-      </c>
-      <c r="K18" s="1">
-        <v>8</v>
-      </c>
-      <c r="L18" s="1">
-        <v>9</v>
-      </c>
-      <c r="M18" s="1">
-        <v>10</v>
-      </c>
-      <c r="N18" s="1">
-        <v>11</v>
-      </c>
-      <c r="O18" s="1">
-        <v>12</v>
-      </c>
-      <c r="P18" s="1">
-        <v>13</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>14</v>
-      </c>
-      <c r="R18" s="1">
-        <v>15</v>
-      </c>
-      <c r="S18" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5">
-        <v>1</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5">
-        <v>2</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>8</v>
+      <c r="E14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="10">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
@@ -1266,10 +981,8 @@
     <mergeCell ref="C6:S6"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:S8"/>
-    <mergeCell ref="C9:S9"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1294,56 +1007,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1359,84 +1072,84 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
